--- a/GaN_Inverter/Project Outputs for GanInverter/Rev02/BOM_JLC/BOM_JLC_GanInverter_Inverter_V1_Rev02.xlsx
+++ b/GaN_Inverter/Project Outputs for GanInverter/Rev02/BOM_JLC/BOM_JLC_GanInverter_Inverter_V1_Rev02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zeynep\Desktop\Zeynep\software\plugins\github\uz_d_gan_inverter_epc\GaN_Inverter\Project Outputs for GanInverter\Rev02\BOM_JLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{079CCF4D-FC4D-40C1-A5DE-8ECA7E21581E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BE7A9B-2AFA-4054-BA0C-8BDAD568DCBA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="7272" xr2:uid="{BDF6A810-E5D0-4002-BF97-1BEAA4FDAE74}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="7272" xr2:uid="{7FCFDD8A-44B1-4A81-826D-17E6A7D51497}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_JLC_GanInverter_Inverter_V1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="203">
   <si>
     <t>Name</t>
   </si>
@@ -195,18 +195,6 @@
     <t>C84269</t>
   </si>
   <si>
-    <t>RGF1M-E3/67A</t>
-  </si>
-  <si>
-    <t>D4A, D4B, D4C, D5A, D5B, D5C</t>
-  </si>
-  <si>
-    <t>FP-GF1M-E3-67A-MFG</t>
-  </si>
-  <si>
-    <t>C3008881</t>
-  </si>
-  <si>
     <t>Littelfuse_PTC_1812</t>
   </si>
   <si>
@@ -291,7 +279,7 @@
     <t>0R</t>
   </si>
   <si>
-    <t>R3, R8, R9, R57A, R57B, R57C, R68, R90, R91A, R91B, R91C, R92A, R92B, R92C, R93A, R93B, R93C, R94, R95, R96</t>
+    <t>R3, R8, R9, R57A, R57B, R57C, R90, R91A, R91B, R91C, R93A, R93B, R93C, R94, R96</t>
   </si>
   <si>
     <t>RES 0603_1608</t>
@@ -570,9 +558,6 @@
     <t>C6730719</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
     <t>U8A, U8B, U8C, U16</t>
   </si>
   <si>
@@ -582,9 +567,6 @@
     <t>C4550714</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>U9A, U9B, U9C, U10A, U10B, U10C</t>
   </si>
   <si>
@@ -615,9 +597,6 @@
     <t>C12401</t>
   </si>
   <si>
-    <t>5V</t>
-  </si>
-  <si>
     <t>U18A, U18B, U18C, U19A, U19B, U19C</t>
   </si>
   <si>
@@ -649,6 +628,15 @@
   </si>
   <si>
     <t>C5116479</t>
+  </si>
+  <si>
+    <t>MAX40056TAUA+T</t>
+  </si>
+  <si>
+    <t>MAX14931FASE+</t>
+  </si>
+  <si>
+    <t>NCP730BMT500TBG</t>
   </si>
 </sst>
 </file>
@@ -1024,12 +1012,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90EE62B7-4195-4595-BEC2-8A6331A94C44}">
-  <dimension ref="A1:D61"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D47293-E9A3-417C-A3C5-D5BCD282D89D}">
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" customWidth="1"/>
     <col min="3" max="3" width="23.44140625" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
@@ -1310,45 +1298,45 @@
       <c r="C20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="C21" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D22" s="1"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
@@ -1400,63 +1388,63 @@
         <v>87</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>101</v>
@@ -1470,133 +1458,133 @@
         <v>103</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="C39" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C40" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>132</v>
@@ -1610,35 +1598,35 @@
         <v>134</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>142</v>
@@ -1652,49 +1640,49 @@
         <v>144</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C46" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>155</v>
@@ -1772,114 +1760,100 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>206</v>
       </c>
     </row>
   </sheetData>
